--- a/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D370B95D-CACD-4470-A98A-00777108B724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8761C5CC-4F9D-4F9F-AB5B-0D51B37FF04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>课程描述</t>
-  </si>
-  <si>
-    <t>课程编号</t>
   </si>
   <si>
     <t>课程简称</t>
@@ -358,43 +355,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.41796875" customWidth="1"/>
-    <col min="2" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19.5234375" customWidth="1"/>
-    <col min="5" max="5" width="16.3671875" customWidth="1"/>
-    <col min="6" max="6" width="30.41796875" customWidth="1"/>
-    <col min="7" max="7" width="28.89453125" customWidth="1"/>
+    <col min="1" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="19.5234375" customWidth="1"/>
+    <col min="4" max="4" width="16.3671875" customWidth="1"/>
+    <col min="5" max="5" width="30.41796875" customWidth="1"/>
+    <col min="6" max="6" width="28.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{42900EF5-3F11-4925-94F6-C7B7AADABB5A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{42900EF5-3F11-4925-94F6-C7B7AADABB5A}">
       <formula1>"基础课程,进阶课程"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8761C5CC-4F9D-4F9F-AB5B-0D51B37FF04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB8AB02-697B-4894-992E-A7405805221E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11895" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="课程" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,10 @@
     <t>课程简称</t>
   </si>
   <si>
-    <t xml:space="preserve"> 课程类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 基础课程</t>
+    <t>课程类型</t>
+  </si>
+  <si>
+    <t>基础课程</t>
   </si>
 </sst>
 </file>

--- a/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB8AB02-697B-4894-992E-A7405805221E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEF90D7-17EC-4442-B33B-AD7DFFB3BA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11895" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>基础课程</t>
+  </si>
+  <si>
+    <t>CatNo</t>
   </si>
 </sst>
 </file>
@@ -355,39 +358,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.5234375" customWidth="1"/>
-    <col min="4" max="4" width="16.3671875" customWidth="1"/>
-    <col min="5" max="5" width="30.41796875" customWidth="1"/>
-    <col min="6" max="6" width="28.89453125" customWidth="1"/>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="19.5234375" customWidth="1"/>
+    <col min="5" max="5" width="16.3671875" customWidth="1"/>
+    <col min="6" max="6" width="30.41796875" customWidth="1"/>
+    <col min="7" max="7" width="28.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{42900EF5-3F11-4925-94F6-C7B7AADABB5A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{42900EF5-3F11-4925-94F6-C7B7AADABB5A}">
       <formula1>"基础课程,进阶课程"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEF90D7-17EC-4442-B33B-AD7DFFB3BA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC20FA2A-D953-46DF-A8DD-7265885158BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11895" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>CatNo</t>
+  </si>
+  <si>
+    <t>Modality</t>
   </si>
 </sst>
 </file>
@@ -358,42 +361,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19.5234375" customWidth="1"/>
-    <col min="5" max="5" width="16.3671875" customWidth="1"/>
-    <col min="6" max="6" width="30.41796875" customWidth="1"/>
-    <col min="7" max="7" width="28.89453125" customWidth="1"/>
+    <col min="1" max="1" width="20.9453125" customWidth="1"/>
+    <col min="2" max="2" width="24.62890625" customWidth="1"/>
+    <col min="3" max="3" width="30.3125" customWidth="1"/>
+    <col min="4" max="4" width="27.26171875" customWidth="1"/>
+    <col min="5" max="5" width="19.5234375" customWidth="1"/>
+    <col min="6" max="6" width="16.3671875" customWidth="1"/>
+    <col min="7" max="7" width="30.41796875" customWidth="1"/>
+    <col min="8" max="8" width="28.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{42900EF5-3F11-4925-94F6-C7B7AADABB5A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{42900EF5-3F11-4925-94F6-C7B7AADABB5A}">
       <formula1>"基础课程,进阶课程"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/trainV2/course/APM_ZKB_Train_Course_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC20FA2A-D953-46DF-A8DD-7265885158BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1602F6B-B3C0-4FC7-9274-69DF1A72CA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11895" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>课程名称</t>
   </si>
   <si>
@@ -44,13 +41,16 @@
   </si>
   <si>
     <t>Modality</t>
+  </si>
+  <si>
+    <t>ps:基础课程请填写CatNo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,13 +58,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -79,8 +92,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -376,28 +390,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
